--- a/PCB/Gerbers/Twin_PLL_GPSDO-JLCPCB-BOM_v_1_1.xlsx
+++ b/PCB/Gerbers/Twin_PLL_GPSDO-JLCPCB-BOM_v_1_1.xlsx
@@ -536,7 +536,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C16, C17, C19, C22, C26, C27, C29, C70, C71, C73</t>
+          <t>C17, C19, C22, C26, C27, C29, C70, C71, C73</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
